--- a/Result/profitability/2312.xlsx
+++ b/Result/profitability/2312.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>0.25625</v>
+        <v>0.255</v>
       </c>
       <c r="N2" t="n">
-        <v>6.5375</v>
+        <v>6.56875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>0.26</v>
+        <v>0.2825</v>
       </c>
       <c r="N3" t="n">
-        <v>6.66125</v>
+        <v>6.8575</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.25</v>
+        <v>0.24875</v>
       </c>
       <c r="N4" t="n">
-        <v>6.65875</v>
+        <v>6.71875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.52</v>
       </c>
       <c r="M5" t="n">
-        <v>0.14125</v>
+        <v>0.15875</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2575</v>
+        <v>6.305000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.12375</v>
+        <v>0.12875</v>
       </c>
       <c r="N6" t="n">
-        <v>6.1425</v>
+        <v>6.12375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03125000000000003</v>
+        <v>0.04875000000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>6.19</v>
+        <v>6.38125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.28</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02874999999999998</v>
+        <v>-0.02999999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>6.685</v>
+        <v>6.6875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.22</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.09249999999999997</v>
+        <v>-0.09249999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>6.96625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2312</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>39427</v>
+      </c>
+      <c r="D75" t="n">
+        <v>36709</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2718</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1234</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-134</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1099</v>
+      </c>
+      <c r="K75" t="n">
+        <v>519</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.009999999999999953</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.02857142857142847</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.002911208151382683</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.3799999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05837173579109067</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
